--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -441,92 +441,92 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18559245690</t>
+          <t>18180873861</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kap</t>
+          <t>idh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[6, 3, 2, 4]</t>
+          <t>[7, 1, 4, 6, 2, 5]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18149006829</t>
+          <t>18621761718</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ice</t>
+          <t>lyl</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[1, 7, 2]</t>
+          <t>[1, 3, 5, 2]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18558598638</t>
+          <t>18827226649</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>epk</t>
+          <t>iwy</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[4, 1, 3]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18260791573</t>
+          <t>18684327394</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cip</t>
+          <t>cgn</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[4, 1, 7, 3, 2]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18664831428</t>
+          <t>18959171344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>khi</t>
+          <t>pwb</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -534,107 +534,107 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[6, 7, 3]</t>
+          <t>[3, 7]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18923750505</t>
+          <t>18171149417</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ldm</t>
+          <t>qat</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[4, 5, 6]</t>
+          <t>[4, 6, 3, 7]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18741595465</t>
+          <t>18675904370</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rvg</t>
+          <t>tns</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[1, 6, 2, 4, 7, 5]</t>
+          <t>[1, 5, 4, 7, 3, 6]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18656390677</t>
+          <t>18565715886</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>obq</t>
+          <t>eyp</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[5, 4, 2, 3, 7, 1]</t>
+          <t>[7, 1, 5]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18748087067</t>
+          <t>18162065351</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mwu</t>
+          <t>svr</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[4, 7, 2, 1, 5, 6, 3]</t>
+          <t>[5, 4, 7, 1, 6, 3]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18189837236</t>
+          <t>18120513379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ahd</t>
+          <t>syd</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[5, 2, 3, 4, 7, 6, 1]</t>
+          <t>[7, 1, 4, 3, 6]</t>
         </is>
       </c>
     </row>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -441,200 +441,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18180873861</t>
+          <t>18136806047</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>idh</t>
+          <t>qhd</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 6, 2, 5]</t>
+          <t>[1]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18621761718</t>
+          <t>18402563540</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lyl</t>
+          <t>ihx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[1, 3, 5, 2]</t>
+          <t>[2, 4, 6, 7, 5]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18827226649</t>
+          <t>18366315786</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>iwy</t>
+          <t>htd</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[4, 1, 3]</t>
+          <t>[7, 1, 4, 3]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18684327394</t>
+          <t>18479137622</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cgn</t>
+          <t>hpj</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[4, 1, 7, 3, 2]</t>
+          <t>[4]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18959171344</t>
+          <t>18919249473</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pwb</t>
+          <t>esb</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[3, 7]</t>
+          <t>[5, 6, 1, 2, 7, 3]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18171149417</t>
+          <t>18909830252</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>qat</t>
+          <t>zkm</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[4, 6, 3, 7]</t>
+          <t>[1, 7, 6, 2, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18675904370</t>
+          <t>18156271064</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tns</t>
+          <t>xob</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[1, 5, 4, 7, 3, 6]</t>
+          <t>[2]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18565715886</t>
+          <t>18608518361</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>eyp</t>
+          <t>rkn</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[7, 1, 5]</t>
+          <t>[1, 7]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18162065351</t>
+          <t>18765085278</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>svr</t>
+          <t>vqx</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[5, 4, 7, 1, 6, 3]</t>
+          <t>[1, 3, 7, 2, 4, 5]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18120513379</t>
+          <t>18772019349</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>syd</t>
+          <t>lbg</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 3, 6]</t>
+          <t>[6, 7, 1]</t>
         </is>
       </c>
     </row>

--- a/data/data.xlsx
+++ b/data/data.xlsx
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18136806047</t>
+          <t>18590594110</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>qhd</t>
+          <t>pgq</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -454,187 +454,187 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[1]</t>
+          <t>[7]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18402563540</t>
+          <t>18454764706</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ihx</t>
+          <t>wsa</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[2, 4, 6, 7, 5]</t>
+          <t>[3, 4, 2, 7, 1, 5]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18366315786</t>
+          <t>18181141347</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>htd</t>
+          <t>kfm</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 3]</t>
+          <t>[1, 7, 3, 2]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18479137622</t>
+          <t>18221919157</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hpj</t>
+          <t>atq</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[4]</t>
+          <t>[7, 5, 3, 4]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18919249473</t>
+          <t>18819490071</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>esb</t>
+          <t>yyb</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[5, 6, 1, 2, 7, 3]</t>
+          <t>[5]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18909830252</t>
+          <t>18307049455</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zkm</t>
+          <t>hcp</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[1, 7, 6, 2, 3, 4]</t>
+          <t>[4, 5, 7, 1, 3]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18156271064</t>
+          <t>18981410421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>xob</t>
+          <t>cem</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[2]</t>
+          <t>[5, 6, 7, 1, 3, 2, 4]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18608518361</t>
+          <t>18853632276</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rkn</t>
+          <t>ayz</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[1, 7]</t>
+          <t>[6, 7, 1, 5, 3, 4, 2]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18765085278</t>
+          <t>18762803366</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vqx</t>
+          <t>sdl</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 2, 4, 5]</t>
+          <t>[2, 4, 1, 7]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18772019349</t>
+          <t>18606231256</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lbg</t>
+          <t>xqc</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[6, 7, 1]</t>
+          <t>[5, 4, 7]</t>
         </is>
       </c>
     </row>
